--- a/data/trans_dic/P79_n_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P79_n_R2-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,57</t>
+          <t>0,77; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,13</t>
+          <t>0,61; 2,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,15</t>
+          <t>0,85; 2,33</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,71</t>
+          <t>0,89; 3,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,93</t>
+          <t>0,83; 3,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,9</t>
+          <t>1,06; 2,69</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,99</t>
+          <t>4,36; 8,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,44</t>
+          <t>0,95; 4,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,47</t>
+          <t>3,61; 6,92</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,17</t>
+          <t>3,56; 6,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,1</t>
+          <t>1,77; 3,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,24</t>
+          <t>2,88; 4,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,7</t>
+          <t>3,99; 8,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,68</t>
+          <t>5,74; 9,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,46</t>
+          <t>5,58; 8,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,62</t>
+          <t>0,81; 7,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,96</t>
+          <t>4,19; 7,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,74</t>
+          <t>3,86; 6,71</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,44</t>
+          <t>3,39; 4,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,31</t>
+          <t>3,46; 4,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,14</t>
+          <t>3,66; 4,58</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>15198</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2903; 12990</t>
+          <t>4241; 17439</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1999; 9524</t>
+          <t>2995; 12460</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6909; 20458</t>
+          <t>8816; 24218</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>16463</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4300; 16767</t>
+          <t>4284; 17049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3059; 11221</t>
+          <t>3522; 13396</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8865; 24236</t>
+          <t>9584; 24395</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>29420</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>33800</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8553; 46732</t>
+          <t>20579; 41391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1588; 7413</t>
+          <t>1786; 8705</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11877; 45647</t>
+          <t>23794; 45613</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>45981</t>
+          <t>53028</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65385</t>
+          <t>74853</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33641; 63828</t>
+          <t>40296; 71047</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10243; 30294</t>
+          <t>15252; 32163</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45733; 85363</t>
+          <t>57479; 95468</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>62175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78897</t>
+          <t>95256</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19059; 41314</t>
+          <t>22639; 46309</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35101; 64586</t>
+          <t>47707; 76713</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58888; 98242</t>
+          <t>78036; 114097</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>43908</t>
+          <t>47025</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>54408</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1318; 13519</t>
+          <t>1912; 17150</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31924; 60624</t>
+          <t>35363; 61695</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35659; 67508</t>
+          <t>41770; 72589</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>121447</t>
+          <t>141182</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>127930</t>
+          <t>148795</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249377</t>
+          <t>289978</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>94948; 149754</t>
+          <t>116576; 166321</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>102037; 154268</t>
+          <t>125823; 172804</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>209392; 287950</t>
+          <t>259040; 324484</t>
         </is>
       </c>
     </row>
